--- a/src/nodes/HPC/compressor_stage_2_blade_stator_coordinates_foil.xlsx
+++ b/src/nodes/HPC/compressor_stage_2_blade_stator_coordinates_foil.xlsx
@@ -1023,7 +1023,7 @@
         <v>0.00062001068411817882</v>
       </c>
       <c r="B2">
-        <v>0.00045591286970083353</v>
+        <v>0.00050179366032557867</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0012400213682363576</v>
       </c>
       <c r="B3">
-        <v>0.000756188372293624</v>
+        <v>0.00081942946207367814</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0018600320523545367</v>
       </c>
       <c r="B4">
-        <v>0.0010238369145167718</v>
+        <v>0.0011004702350737787</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0024800427364727153</v>
       </c>
       <c r="B5">
-        <v>0.0012659063127057311</v>
+        <v>0.0013533278191663941</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0031000534205908939</v>
       </c>
       <c r="B6">
-        <v>0.0014853846344260466</v>
+        <v>0.0015815459860570869</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.0037200641047090734</v>
       </c>
       <c r="B7">
-        <v>0.001684044257953771</v>
+        <v>0.001787214035791036</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.004340074788827252</v>
       </c>
       <c r="B8">
-        <v>0.0018629930643419231</v>
+        <v>0.0019716259283640136</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.0049600854729454306</v>
       </c>
       <c r="B9">
-        <v>0.0020238434704335779</v>
+        <v>0.0021366854149430865</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.0055800961570636092</v>
       </c>
       <c r="B10">
-        <v>0.0021683142499960726</v>
+        <v>0.0022844258881090157</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.0062001068411817878</v>
       </c>
       <c r="B11">
-        <v>0.0022980450687037491</v>
+        <v>0.0024167895149260631</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.0068201175252999673</v>
       </c>
       <c r="B12">
-        <v>0.0024139606345916519</v>
+        <v>0.0025348622769046877</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.0074401282094181467</v>
       </c>
       <c r="B13">
-        <v>0.0025142049332306337</v>
+        <v>0.0026363966388566447</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.0080601388935363245</v>
       </c>
       <c r="B14">
-        <v>0.0025976997127109785</v>
+        <v>0.0027200800486575508</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.0086801495776545039</v>
       </c>
       <c r="B15">
-        <v>0.0026692584936648888</v>
+        <v>0.0027916734031371822</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.0093001602617726817</v>
       </c>
       <c r="B16">
-        <v>0.0027332956550435387</v>
+        <v>0.002856460010232582</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.0099201709458908612</v>
       </c>
       <c r="B17">
-        <v>0.0027867372365320683</v>
+        <v>0.0029107393733557043</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.010540181630009041</v>
       </c>
       <c r="B18">
-        <v>0.0028255886141533215</v>
+        <v>0.002949707901962635</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.011160192314127218</v>
       </c>
       <c r="B19">
-        <v>0.0028496608485469844</v>
+        <v>0.0029731334342110822</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.011780202998245398</v>
       </c>
       <c r="B20">
-        <v>0.0028597164215069548</v>
+        <v>0.0029819266654341576</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.012400213682363576</v>
       </c>
       <c r="B21">
-        <v>0.0028565178148271292</v>
+        <v>0.0029769982909649737</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.013020224366481755</v>
       </c>
       <c r="B22">
-        <v>0.002840688648060728</v>
+        <v>0.0029590937701946228</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.013640235050599935</v>
       </c>
       <c r="B23">
-        <v>0.0028122970917982635</v>
+        <v>0.0029282976187461158</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.014260245734718114</v>
       </c>
       <c r="B24">
-        <v>0.0027712724543895689</v>
+        <v>0.0028845291163004435</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.014880256418836294</v>
       </c>
       <c r="B25">
-        <v>0.0027175440441844795</v>
+        <v>0.0028277075425385974</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.01550026710295447</v>
       </c>
       <c r="B26">
-        <v>0.0026510125390063854</v>
+        <v>0.0027577192142896286</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.016120277787072649</v>
       </c>
       <c r="B27">
-        <v>0.0025714640945728963</v>
+        <v>0.00267431859697483</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.016740288471190828</v>
       </c>
       <c r="B28">
-        <v>0.0024786562360751773</v>
+        <v>0.0025772271931635547</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.017360299155309008</v>
       </c>
       <c r="B29">
-        <v>0.0023723464887043938</v>
+        <v>0.0024661665054251563</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.017980309839427187</v>
       </c>
       <c r="B30">
-        <v>0.0022523830139567027</v>
+        <v>0.0023409683502232928</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.018600320523545363</v>
       </c>
       <c r="B31">
-        <v>0.00211897651854823</v>
+        <v>0.0022019057995988382</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.019220331207663543</v>
       </c>
       <c r="B32">
-        <v>0.0019724283455000886</v>
+        <v>0.0020493622394869709</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.019840341891781722</v>
       </c>
       <c r="B33">
-        <v>0.0018130398378333969</v>
+        <v>0.0018837210558228694</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.020460352575899902</v>
       </c>
       <c r="B34">
-        <v>0.0016409439188600397</v>
+        <v>0.0017051654625352608</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.021080363260018081</v>
       </c>
       <c r="B35">
-        <v>0.0014555998330549832</v>
+        <v>0.0015130779855270639</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.021700373944136257</v>
       </c>
       <c r="B36">
-        <v>0.001256298405183964</v>
+        <v>0.001306640978694747</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.022320384628254437</v>
       </c>
       <c r="B37">
-        <v>0.0010423304600127158</v>
+        <v>0.0010850367959347759</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.022940395312372616</v>
       </c>
       <c r="B38">
-        <v>0.00081258666603134793</v>
+        <v>0.00084696973827568574</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.023560405996490796</v>
       </c>
       <c r="B39">
-        <v>0.00056435706662745836</v>
+        <v>0.00058923189527427958</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.024180416680608975</v>
       </c>
       <c r="B40">
-        <v>0.00029453154891301834</v>
+        <v>0.00030813730361942723</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.024180416680608975</v>
       </c>
       <c r="B43">
-        <v>0.00015847400184892959</v>
+        <v>0.00014486824714252076</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.023560405996490796</v>
       </c>
       <c r="B44">
-        <v>0.00031560878015924552</v>
+        <v>0.00029073395151242424</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.022940395312372616</v>
       </c>
       <c r="B45">
-        <v>0.000468755943587967</v>
+        <v>0.000434372871343629</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.022320384628254437</v>
       </c>
       <c r="B46">
-        <v>0.00061526710079211431</v>
+        <v>0.00057256076487005407</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.021700373944136257</v>
       </c>
       <c r="B47">
-        <v>0.000752872670076134</v>
+        <v>0.000702530096565351</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.021080363260018081</v>
       </c>
       <c r="B48">
-        <v>0.00088081830833417959</v>
+        <v>0.000823340155862099</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.020460352575899902</v>
       </c>
       <c r="B49">
-        <v>0.00099872848210783276</v>
+        <v>0.00093450693843261177</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.019840341891781722</v>
       </c>
       <c r="B50">
-        <v>0.0011062276579386732</v>
+        <v>0.0010355464399492006</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.019220331207663543</v>
       </c>
       <c r="B51">
-        <v>0.00120308940563127</v>
+        <v>0.0011261555116443879</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.018600320523545363</v>
       </c>
       <c r="B52">
-        <v>0.0012896837080421445</v>
+        <v>0.0012067544269915359</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.017980309839427187</v>
       </c>
       <c r="B53">
-        <v>0.0013665296512908062</v>
+        <v>0.0012779443150242166</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.017360299155309008</v>
       </c>
       <c r="B54">
-        <v>0.0014341463214967657</v>
+        <v>0.001340326304776003</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.016740288471190828</v>
       </c>
       <c r="B55">
-        <v>0.0014929466651914</v>
+        <v>0.0013943757081030224</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.016120277787072649</v>
       </c>
       <c r="B56">
-        <v>0.0015429190705535565</v>
+        <v>0.001440064568151623</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.01550026710295447</v>
       </c>
       <c r="B57">
-        <v>0.0015839457861739513</v>
+        <v>0.0014772391108907083</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.014880256418836294</v>
       </c>
       <c r="B58">
-        <v>0.0016159090606432996</v>
+        <v>0.0015057455622891818</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.014260245734718114</v>
       </c>
       <c r="B59">
-        <v>0.0016387058352808188</v>
+        <v>0.0015254491733699442</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.013640235050599935</v>
       </c>
       <c r="B60">
-        <v>0.0016522918223197366</v>
+        <v>0.0015362912953718842</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.013020224366481755</v>
       </c>
       <c r="B61">
-        <v>0.0016566374267217819</v>
+        <v>0.0015382323045878875</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.012400213682363576</v>
       </c>
       <c r="B62">
-        <v>0.001651713053448684</v>
+        <v>0.00153123257731084</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.011780202998245398</v>
       </c>
       <c r="B63">
-        <v>0.0016376139822349269</v>
+        <v>0.0015154037383077242</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.011160192314127218</v>
       </c>
       <c r="B64">
-        <v>0.0016149349919060095</v>
+        <v>0.0014914624062419123</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.010540181630009041</v>
       </c>
       <c r="B65">
-        <v>0.0015843957360601863</v>
+        <v>0.0014602764482508732</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.0099201709458908612</v>
       </c>
       <c r="B66">
-        <v>0.0015467158682957109</v>
+        <v>0.0014227137314720753</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.0093001602617726817</v>
       </c>
       <c r="B67">
-        <v>0.0015016521031531044</v>
+        <v>0.0013784877479640608</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.0086801495776545039</v>
       </c>
       <c r="B68">
-        <v>0.0014451093989419565</v>
+        <v>0.0013226944894696635</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.0080601388935363245</v>
       </c>
       <c r="B69">
-        <v>0.0013738963532452574</v>
+        <v>0.0012515160172986855</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.0074401282094181467</v>
       </c>
       <c r="B70">
-        <v>0.0012922878769705268</v>
+        <v>0.0011700961713445163</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.0068201175252999673</v>
       </c>
       <c r="B71">
-        <v>0.0012049442114612959</v>
+        <v>0.0010840425691482603</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.0062001068411817878</v>
       </c>
       <c r="B72">
-        <v>0.0011106006064806131</v>
+        <v>0.00099185616025829963</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.0055800961570636092</v>
       </c>
       <c r="B73">
-        <v>0.0010071978688666427</v>
+        <v>0.00089108623075369992</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.0049600854729454306</v>
       </c>
       <c r="B74">
-        <v>0.00089542402533849218</v>
+        <v>0.00078258208082898368</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.004340074788827252</v>
       </c>
       <c r="B75">
-        <v>0.00077666442412101689</v>
+        <v>0.00066803156009892625</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.0037200641047090734</v>
       </c>
       <c r="B76">
-        <v>0.00065234647958112139</v>
+        <v>0.00054917670174385645</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0031000534205908939</v>
       </c>
       <c r="B77">
-        <v>0.00052377111811564262</v>
+        <v>0.00042760976648460221</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0024800427364727153</v>
       </c>
       <c r="B78">
-        <v>0.00039169124809909905</v>
+        <v>0.00030426974163843591</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0018600320523545367</v>
       </c>
       <c r="B79">
-        <v>0.00025750370894670274</v>
+        <v>0.00018087038838969591</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0012400213682363576</v>
       </c>
       <c r="B80">
-        <v>0.00012377747449308175</v>
+        <v>6.0536384713027539E-05</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.00062001068411817882</v>
       </c>
       <c r="B81">
-        <v>-2.8950365466187712E-06</v>
+        <v>-4.8775827171363983E-05</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.00067141905650108455</v>
       </c>
       <c r="B2">
-        <v>0.00058695324703808311</v>
+        <v>0.00068632326740024352</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0013428381130021691</v>
       </c>
       <c r="B3">
-        <v>0.00094402000714864458</v>
+        <v>0.0010809894946748658</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0020142571695032536</v>
       </c>
       <c r="B4">
-        <v>0.0012575658009956433</v>
+        <v>0.0014235405917627114</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0026856762260043382</v>
       </c>
       <c r="B5">
-        <v>0.0015381584014313439</v>
+        <v>0.0017274985753646496</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0033570952825054223</v>
       </c>
       <c r="B6">
-        <v>0.0017902203012563015</v>
+        <v>0.001998489499313139</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.0040285143390065073</v>
       </c>
       <c r="B7">
-        <v>0.0020163423892335746</v>
+        <v>0.0022397906512371351</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.0046999333955075918</v>
       </c>
       <c r="B8">
-        <v>0.0022181135146246305</v>
+        <v>0.0024533938958666416</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.0053713524520086764</v>
       </c>
       <c r="B9">
-        <v>0.0023978988020360377</v>
+        <v>0.0026422953386024324</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.00604277150850976</v>
       </c>
       <c r="B10">
-        <v>0.0025582298561531418</v>
+        <v>0.0028097079951838167</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.0067141905650108446</v>
       </c>
       <c r="B11">
-        <v>0.0027015279266313064</v>
+        <v>0.0029587082820334821</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.00738560962151193</v>
       </c>
       <c r="B12">
-        <v>0.0028291348746433808</v>
+        <v>0.0030909873513525637</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.0080570286780130146</v>
       </c>
       <c r="B13">
-        <v>0.0029381853624621417</v>
+        <v>0.003202831897772609</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.0087284477345141</v>
       </c>
       <c r="B14">
-        <v>0.0030269974702426669</v>
+        <v>0.0032920525468738025</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.0093998667910151837</v>
       </c>
       <c r="B15">
-        <v>0.0031028301485693183</v>
+        <v>0.0033679601056004669</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.010071285847516267</v>
       </c>
       <c r="B16">
-        <v>0.00317234073183618</v>
+        <v>0.0034390938613349281</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.010742704904017353</v>
       </c>
       <c r="B17">
-        <v>0.0032308392192469536</v>
+        <v>0.0034994068418473866</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.011414123960518437</v>
       </c>
       <c r="B18">
-        <v>0.0032722441149961941</v>
+        <v>0.0035410654667864193</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.01208554301701952</v>
       </c>
       <c r="B19">
-        <v>0.0032962552784322617</v>
+        <v>0.0035636759829262366</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.012756962073520606</v>
       </c>
       <c r="B20">
-        <v>0.0033040179076919657</v>
+        <v>0.0035687045938224567</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.013428381130021689</v>
       </c>
       <c r="B21">
-        <v>0.0032966772009121168</v>
+        <v>0.0035576175030306977</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.014099800186522774</v>
       </c>
       <c r="B22">
-        <v>0.0032751713520064907</v>
+        <v>0.0035316167889140968</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.01477121924302386</v>
       </c>
       <c r="B23">
-        <v>0.0032396105379967287</v>
+        <v>0.0034908480290658677</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.015442638299524945</v>
       </c>
       <c r="B24">
-        <v>0.0031898979316814374</v>
+        <v>0.0034351926758867412</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.016114057356026029</v>
       </c>
       <c r="B25">
-        <v>0.0031259367058592232</v>
+        <v>0.00336453218177745</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.01678547641252711</v>
       </c>
       <c r="B26">
-        <v>0.0030475901481226081</v>
+        <v>0.0032786987308495046</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.0174568954690282</v>
       </c>
       <c r="B27">
-        <v>0.0029545620052397609</v>
+        <v>0.0031773274340575397</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.018128314525529283</v>
       </c>
       <c r="B28">
-        <v>0.0028465161387727683</v>
+        <v>0.0030600041340669674</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.018799733582030367</v>
       </c>
       <c r="B29">
-        <v>0.0027231164102837135</v>
+        <v>0.0029263146735432014</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.019471152638531452</v>
       </c>
       <c r="B30">
-        <v>0.0025841680442064466</v>
+        <v>0.0027760288763485196</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.020142571695032533</v>
       </c>
       <c r="B31">
-        <v>0.0024300417164618768</v>
+        <v>0.0026096524911326554</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.020813990751533618</v>
       </c>
       <c r="B32">
-        <v>0.0022612494658426768</v>
+        <v>0.002427875247742206</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.021485409808034706</v>
       </c>
       <c r="B33">
-        <v>0.0020783033311415214</v>
+        <v>0.0022313868760237688</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.02215682886453579</v>
       </c>
       <c r="B34">
-        <v>0.0018814650148632171</v>
+        <v>0.0020205579994390798</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.022828247921036875</v>
       </c>
       <c r="B35">
-        <v>0.0016699948743611032</v>
+        <v>0.0017944828159104256</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.023499666977537956</v>
       </c>
       <c r="B36">
-        <v>0.0014429029307006529</v>
+        <v>0.0015519364169752335</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.02417108603403904</v>
       </c>
       <c r="B37">
-        <v>0.0011991992049473366</v>
+        <v>0.0012916938941709259</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.024842505090540125</v>
       </c>
       <c r="B38">
-        <v>0.00093729267281795776</v>
+        <v>0.0010117605828628817</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.025513924147041213</v>
       </c>
       <c r="B39">
-        <v>0.00065318812863463958</v>
+        <v>0.00070706279372828649</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.026185343203542297</v>
       </c>
       <c r="B40">
-        <v>0.00034228932137083529</v>
+        <v>0.00037175708127227923</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2001,7 +2001,7 @@
         <v>0.026856762260043378</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>-9.3178111962450358E-20</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.026185343203542297</v>
       </c>
       <c r="B43">
-        <v>0.00013601500206072802</v>
+        <v>0.00010654724215928405</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.025513924147041213</v>
       </c>
       <c r="B44">
-        <v>0.00027606547297911115</v>
+        <v>0.00022219080788546421</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.024842505090540125</v>
       </c>
       <c r="B45">
-        <v>0.00041601730250349119</v>
+        <v>0.00034154939245856751</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.02417108603403904</v>
       </c>
       <c r="B46">
-        <v>0.0005517363803822108</v>
+        <v>0.00045924169115862148</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.023499666977537956</v>
       </c>
       <c r="B47">
-        <v>0.00067966852677858812</v>
+        <v>0.00057063504050400759</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.022828247921036875</v>
       </c>
       <c r="B48">
-        <v>0.00079857928351584481</v>
+        <v>0.0006740913419665223</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.02215682886453579</v>
       </c>
       <c r="B49">
-        <v>0.00090781412283217982</v>
+        <v>0.00076872113825631741</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.021485409808034706</v>
       </c>
       <c r="B50">
-        <v>0.0010067185169657905</v>
+        <v>0.00085363497208354325</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.020813990751533618</v>
       </c>
       <c r="B51">
-        <v>0.0010948689925459742</v>
+        <v>0.00092824321064644509</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.020142571695032533</v>
       </c>
       <c r="B52">
-        <v>0.0011727662937664244</v>
+        <v>0.0009931555190956455</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.019471152638531452</v>
       </c>
       <c r="B53">
-        <v>0.0012411422192119337</v>
+        <v>0.0010492813870698605</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.018799733582030367</v>
       </c>
       <c r="B54">
-        <v>0.0013007285674672964</v>
+        <v>0.0010975303042078082</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.018128314525529283</v>
       </c>
       <c r="B55">
-        <v>0.0013521001717133746</v>
+        <v>0.0011386121764191757</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.0174568954690282</v>
       </c>
       <c r="B56">
-        <v>0.0013952040035153149</v>
+        <v>0.0011724385746975368</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.01678547641252711</v>
       </c>
       <c r="B57">
-        <v>0.0014298300690343334</v>
+        <v>0.0011987214863074371</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.016114057356026029</v>
       </c>
       <c r="B58">
-        <v>0.0014557683744316461</v>
+        <v>0.0012171728985134209</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.015442638299524945</v>
       </c>
       <c r="B59">
-        <v>0.001472834722244312</v>
+        <v>0.0012275399780390082</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.01477121924302386</v>
       </c>
       <c r="B60">
-        <v>0.0014809481005127558</v>
+        <v>0.0012297106094436168</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.014099800186522774</v>
       </c>
       <c r="B61">
-        <v>0.0014800532936532448</v>
+        <v>0.0012236078567456382</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.013428381130021689</v>
       </c>
       <c r="B62">
-        <v>0.0014700950860820463</v>
+        <v>0.0012091547839634649</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.012756962073520606</v>
       </c>
       <c r="B63">
-        <v>0.0014512111047785242</v>
+        <v>0.0011865244186480327</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.01208554301701952</v>
       </c>
       <c r="B64">
-        <v>0.0014243103469744297</v>
+        <v>0.001156889642480454</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.011414123960518437</v>
       </c>
       <c r="B65">
-        <v>0.0013904946524646114</v>
+        <v>0.0011216733006743852</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.010742704904017353</v>
       </c>
       <c r="B66">
-        <v>0.0013508658610439166</v>
+        <v>0.001082298238443483</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.010071285847516267</v>
       </c>
       <c r="B67">
-        <v>0.0013050688253449429</v>
+        <v>0.0010383156958461948</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.0093998667910151837</v>
       </c>
       <c r="B68">
-        <v>0.0012469204493512807</v>
+        <v>0.00098179049232013232</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.0087284477345141</v>
       </c>
       <c r="B69">
-        <v>0.0011716119338247215</v>
+        <v>0.0009065568571935866</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.0080570286780130146</v>
       </c>
       <c r="B70">
-        <v>0.0010856596152888694</v>
+        <v>0.00082101307997840215</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.00738560962151193</v>
       </c>
       <c r="B71">
-        <v>0.00099616753767910117</v>
+        <v>0.0007343150609699186</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.0067141905650108446</v>
       </c>
       <c r="B72">
-        <v>0.00090126543881607912</v>
+        <v>0.0006440850834139039</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.00604277150850976</v>
       </c>
       <c r="B73">
-        <v>0.00079788288293841973</v>
+        <v>0.0005464047439077452</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.0053713524520086764</v>
       </c>
       <c r="B74">
-        <v>0.00068712304607127428</v>
+        <v>0.00044272650950487964</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.0046999333955075918</v>
       </c>
       <c r="B75">
-        <v>0.00057115084593055063</v>
+        <v>0.00033587046468853938</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.0040285143390065073</v>
       </c>
       <c r="B76">
-        <v>0.00045220455520864755</v>
+        <v>0.00022875629320508685</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0033570952825054223</v>
       </c>
       <c r="B77">
-        <v>0.00033233591485843831</v>
+        <v>0.00012406671680160095</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0026856762260043382</v>
       </c>
       <c r="B78">
-        <v>0.00021277718389820348</v>
+        <v>2.3437009964897833E-05</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0020142571695032536</v>
       </c>
       <c r="B79">
-        <v>9.5742265626166386E-05</v>
+        <v>-7.0232525140901563E-05</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0013428381130021691</v>
       </c>
       <c r="B80">
-        <v>-1.4766405534903893E-05</v>
+        <v>-0.00015173589306112503</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.00067141905650108455</v>
       </c>
       <c r="B81">
-        <v>-0.0001086368954970405</v>
+        <v>-0.00020800691585920093</v>
       </c>
     </row>
     <row r="82" spans="1:2">
